--- a/artfynd/A 18475-2026 artfynd.xlsx
+++ b/artfynd/A 18475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132614868</v>
+        <v>132614862</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515678</v>
+        <v>515680</v>
       </c>
       <c r="R2" t="n">
-        <v>7099491</v>
+        <v>7099449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132614839</v>
+        <v>132698216</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515689</v>
+        <v>515581</v>
       </c>
       <c r="R3" t="n">
-        <v>7099467</v>
+        <v>7099414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,34 +852,65 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mindre fruktkropp långt ner på stambasen av en stående död äldre gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132614862</v>
+        <v>132614864</v>
       </c>
       <c r="B4" t="n">
-        <v>91868</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515680</v>
+        <v>515513</v>
       </c>
       <c r="R4" t="n">
-        <v>7099449</v>
+        <v>7099386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132614864</v>
+        <v>132614866</v>
       </c>
       <c r="B5" t="n">
-        <v>92217</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515513</v>
+        <v>515510</v>
       </c>
       <c r="R5" t="n">
-        <v>7099386</v>
+        <v>7099482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132614875</v>
+        <v>132614872</v>
       </c>
       <c r="B6" t="n">
-        <v>91914</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515691</v>
+        <v>515692</v>
       </c>
       <c r="R6" t="n">
-        <v>7099477</v>
+        <v>7099423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1201,7 @@
         <v>132614874</v>
       </c>
       <c r="B7" t="n">
-        <v>91914</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132614838</v>
+        <v>132614875</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515527</v>
+        <v>515691</v>
       </c>
       <c r="R8" t="n">
-        <v>7099358</v>
+        <v>7099477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132614840</v>
+        <v>132698197</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>91970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1403,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515675</v>
+        <v>515598</v>
       </c>
       <c r="R9" t="n">
-        <v>7099553</v>
+        <v>7099421</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1427,34 +1472,65 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132614869</v>
+        <v>132698198</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>91970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1538,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515670</v>
+        <v>515598</v>
       </c>
       <c r="R10" t="n">
-        <v>7099669</v>
+        <v>7099418</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1524,34 +1607,65 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132614867</v>
+        <v>132614837</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515637</v>
+        <v>515513</v>
       </c>
       <c r="R11" t="n">
-        <v>7099398</v>
+        <v>7099386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132614837</v>
+        <v>132614838</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515513</v>
+        <v>515527</v>
       </c>
       <c r="R12" t="n">
-        <v>7099386</v>
+        <v>7099358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132614863</v>
+        <v>132614839</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515541</v>
+        <v>515689</v>
       </c>
       <c r="R13" t="n">
-        <v>7099360</v>
+        <v>7099467</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1813,11 +1927,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1844,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132614872</v>
+        <v>132614840</v>
       </c>
       <c r="B14" t="n">
-        <v>91914</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515692</v>
+        <v>515675</v>
       </c>
       <c r="R14" t="n">
-        <v>7099423</v>
+        <v>7099553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132698200</v>
+        <v>132614842</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,37 +2061,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515473</v>
+        <v>515511</v>
       </c>
       <c r="R15" t="n">
-        <v>7099399</v>
+        <v>7099483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2023,78 +2129,57 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132698157</v>
+        <v>132698146</v>
       </c>
       <c r="B16" t="n">
-        <v>80467</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2104,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515645</v>
+        <v>515662</v>
       </c>
       <c r="R16" t="n">
-        <v>7099540</v>
+        <v>7099581</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,7 +2229,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Fruktkropp i flera meter av en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2164,22 +2249,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2197,10 +2282,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132698173</v>
+        <v>132698147</v>
       </c>
       <c r="B17" t="n">
-        <v>80438</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2208,26 +2293,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515589</v>
+        <v>515581</v>
       </c>
       <c r="R17" t="n">
-        <v>7099496</v>
+        <v>7099538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,6 +2362,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i en stående lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2290,17 +2384,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2318,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132698202</v>
+        <v>132698159</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>80489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515620</v>
+        <v>515571</v>
       </c>
       <c r="R18" t="n">
-        <v>7099446</v>
+        <v>7099422</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,11 +2488,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2416,17 +2505,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2444,42 +2533,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132698149</v>
+        <v>132698188</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>96410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2812</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2487,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515568</v>
+        <v>515517</v>
       </c>
       <c r="R19" t="n">
-        <v>7099418</v>
+        <v>7099441</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,43 +2610,19 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre bohål, 2 st i en stående död gran med full längd. Ca 40 mm i diameter, på 1,1 meters höjd och på 1,8 meters höjd. I skogsbeståndet runt fyndplatsen finns stående död ved som indikerar medelhögt till mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2579,37 +2640,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132698204</v>
+        <v>132698190</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>96410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2617,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515666</v>
+        <v>515571</v>
       </c>
       <c r="R20" t="n">
-        <v>7099470</v>
+        <v>7099477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,11 +2717,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2673,21 +2730,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2705,32 +2747,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132698159</v>
+        <v>132698200</v>
       </c>
       <c r="B21" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2785,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515571</v>
+        <v>515473</v>
       </c>
       <c r="R21" t="n">
-        <v>7099422</v>
+        <v>7099399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,17 +2840,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2826,14 +2868,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132698203</v>
+        <v>132698201</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2864,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515617</v>
+        <v>515550</v>
       </c>
       <c r="R22" t="n">
-        <v>7099468</v>
+        <v>7099422</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,6 +2942,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,41 +2994,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132698164</v>
+        <v>132698202</v>
       </c>
       <c r="B23" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2989,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515619</v>
+        <v>515620</v>
       </c>
       <c r="R23" t="n">
-        <v>7099475</v>
+        <v>7099446</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,7 +3072,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på en tvåstammig sälg. Fertila bålar med apothecier.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,22 +3092,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3082,41 +3120,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132698156</v>
+        <v>132698203</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3124,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515625</v>
+        <v>515617</v>
       </c>
       <c r="R24" t="n">
-        <v>7099435</v>
+        <v>7099468</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,22 +3213,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3212,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132698195</v>
+        <v>132698204</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3223,54 +3252,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515658</v>
+        <v>515666</v>
       </c>
       <c r="R25" t="n">
-        <v>7099621</v>
+        <v>7099470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3307,7 +3319,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,6 +3335,21 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3340,14 +3367,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132698208</v>
+        <v>132698205</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3378,10 +3405,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515510</v>
+        <v>515651</v>
       </c>
       <c r="R26" t="n">
-        <v>7099459</v>
+        <v>7099534</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,11 +3443,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3448,12 +3470,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3471,41 +3493,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132698198</v>
+        <v>132698206</v>
       </c>
       <c r="B27" t="n">
-        <v>91914</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3513,10 +3531,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515598</v>
+        <v>515629</v>
       </c>
       <c r="R27" t="n">
-        <v>7099418</v>
+        <v>7099630</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3551,11 +3569,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3581,14 +3594,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3606,14 +3614,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132698205</v>
+        <v>132698207</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3644,10 +3652,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515651</v>
+        <v>515553</v>
       </c>
       <c r="R28" t="n">
-        <v>7099534</v>
+        <v>7099497</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,14 +3715,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3732,14 +3735,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132698201</v>
+        <v>132698208</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3770,10 +3773,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515550</v>
+        <v>515510</v>
       </c>
       <c r="R29" t="n">
-        <v>7099422</v>
+        <v>7099459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,7 +3813,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3838,9 +3841,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3858,65 +3866,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132698184</v>
+        <v>132614867</v>
       </c>
       <c r="B30" t="n">
-        <v>58332</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515598</v>
+        <v>515637</v>
       </c>
       <c r="R30" t="n">
-        <v>7099484</v>
+        <v>7099398</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,30 +3948,25 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132698197</v>
+        <v>132614868</v>
       </c>
       <c r="B31" t="n">
-        <v>91914</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3991,41 +3974,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515598</v>
+        <v>515678</v>
       </c>
       <c r="R31" t="n">
-        <v>7099421</v>
+        <v>7099491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,65 +4036,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132698166</v>
+        <v>132614869</v>
       </c>
       <c r="B32" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4144,23 +4089,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515638</v>
+        <v>515670</v>
       </c>
       <c r="R32" t="n">
-        <v>7099445</v>
+        <v>7099669</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,97 +4139,63 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132698145</v>
+        <v>132614870</v>
       </c>
       <c r="B33" t="n">
-        <v>106243</v>
+        <v>80488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515573</v>
+        <v>515623</v>
       </c>
       <c r="R33" t="n">
-        <v>7099479</v>
+        <v>7099680</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,45 +4230,34 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Flera frökapslar och gröna blad på fuktig mark.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132698162</v>
+        <v>132614871</v>
       </c>
       <c r="B34" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,19 +4283,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Skarvhöjden Öst, Jmt</t>
+          <t>Lill-skarvhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515481</v>
+        <v>515503</v>
       </c>
       <c r="R34" t="n">
-        <v>7099415</v>
+        <v>7099481</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,49 +4333,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132698163</v>
+        <v>132698162</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,10 +4389,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515477</v>
+        <v>515481</v>
       </c>
       <c r="R35" t="n">
-        <v>7099420</v>
+        <v>7099415</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4603,10 +4472,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132698216</v>
+        <v>132698163</v>
       </c>
       <c r="B36" t="n">
-        <v>89300</v>
+        <v>80488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4614,30 +4483,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4645,10 +4510,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515581</v>
+        <v>515477</v>
       </c>
       <c r="R36" t="n">
-        <v>7099414</v>
+        <v>7099420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4683,11 +4548,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Mindre fruktkropp långt ner på stambasen av en stående död äldre gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4705,22 +4565,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4738,32 +4593,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132698154</v>
+        <v>132698164</v>
       </c>
       <c r="B37" t="n">
-        <v>80467</v>
+        <v>80488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4780,10 +4635,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515518</v>
+        <v>515619</v>
       </c>
       <c r="R37" t="n">
-        <v>7099436</v>
+        <v>7099475</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4818,6 +4673,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt på en tvåstammig sälg. Fertila bålar med apothecier.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4843,9 +4703,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4863,10 +4728,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132698167</v>
+        <v>132698166</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4893,7 +4758,11 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4901,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515663</v>
+        <v>515638</v>
       </c>
       <c r="R38" t="n">
-        <v>7099628</v>
+        <v>7099445</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4964,9 +4833,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4984,10 +4858,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132698151</v>
+        <v>132698167</v>
       </c>
       <c r="B39" t="n">
-        <v>58119</v>
+        <v>80488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4995,50 +4869,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515579</v>
+        <v>515663</v>
       </c>
       <c r="R39" t="n">
-        <v>7099451</v>
+        <v>7099628</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5079,6 +4940,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5087,9 +4949,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk. Här finns murkna björkhögstubbar för talltitans bohål.</t>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5107,39 +4979,39 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132698176</v>
+        <v>132698169</v>
       </c>
       <c r="B40" t="n">
-        <v>80474</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5149,10 +5021,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515585</v>
+        <v>515625</v>
       </c>
       <c r="R40" t="n">
-        <v>7099498</v>
+        <v>7099628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5237,10 +5109,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132698172</v>
+        <v>132698170</v>
       </c>
       <c r="B41" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5267,11 +5139,7 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5279,10 +5147,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515588</v>
+        <v>515630</v>
       </c>
       <c r="R41" t="n">
-        <v>7099511</v>
+        <v>7099540</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5317,11 +5185,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på en död upplyft sälglåga.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5347,14 +5210,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5372,10 +5230,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132698170</v>
+        <v>132698172</v>
       </c>
       <c r="B42" t="n">
-        <v>80438</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5402,7 +5260,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5410,10 +5272,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515630</v>
+        <v>515588</v>
       </c>
       <c r="R42" t="n">
-        <v>7099540</v>
+        <v>7099511</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5448,6 +5310,11 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en död upplyft sälglåga.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5473,9 +5340,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5493,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132698146</v>
+        <v>132698173</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5504,30 +5376,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5535,10 +5403,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515662</v>
+        <v>515589</v>
       </c>
       <c r="R43" t="n">
-        <v>7099581</v>
+        <v>7099496</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5573,11 +5441,6 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fruktkropp i flera meter av en upplyft granlåga.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5595,22 +5458,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5628,10 +5486,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132614843</v>
+        <v>132698174</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5639,34 +5497,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515448</v>
+        <v>515517</v>
       </c>
       <c r="R44" t="n">
-        <v>7099409</v>
+        <v>7099481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5701,74 +5562,97 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132614847</v>
+        <v>132698154</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515683</v>
+        <v>515518</v>
       </c>
       <c r="R45" t="n">
-        <v>7099444</v>
+        <v>7099436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5803,74 +5687,97 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132614845</v>
+        <v>132698156</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>515482</v>
+        <v>515625</v>
       </c>
       <c r="R46" t="n">
-        <v>7099372</v>
+        <v>7099435</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5905,69 +5812,89 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132698148</v>
+        <v>132698157</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5977,10 +5904,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>515469</v>
+        <v>515645</v>
       </c>
       <c r="R47" t="n">
-        <v>7099391</v>
+        <v>7099540</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6017,7 +5944,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6026,6 +5953,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6036,22 +5964,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6069,45 +5997,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132614846</v>
+        <v>132698158</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lill-skarvhöjden, Jmt</t>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>515485</v>
+        <v>515534</v>
       </c>
       <c r="R48" t="n">
-        <v>7099368</v>
+        <v>7099502</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6142,32 +6077,2952 @@
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132698175</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>515642</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7099645</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132698176</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>515585</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7099498</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132698177</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>515515</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7099482</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132614863</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>515541</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7099360</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132614843</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>515448</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7099409</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132614845</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>515482</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7099372</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132614846</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>515485</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7099368</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132614847</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>515683</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7099444</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132614848</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>515572</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7099501</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132614849</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>515499</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7099470</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132614850</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lill-skarvhöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>515444</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7099428</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132698148</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>515469</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7099391</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132698149</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>515568</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7099418</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre bohål, 2 st i en stående död gran med full längd. Ca 40 mm i diameter, på 1,1 meters höjd och på 1,8 meters höjd. I skogsbeståndet runt fyndplatsen finns stående död ved som indikerar medelhögt till mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132698150</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>515444</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7099420</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran. På/kring fyndplatsen finns stående död ved i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett. Även gott om vindfälld gran här.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132698196</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>515538</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7099497</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färsk spillning i lämplig livsmiljö för järpe.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Flerskiktad granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132698183</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>515624</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7099623</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132698184</v>
+      </c>
+      <c r="B65" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>515598</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7099484</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132698186</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>515479</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7099453</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132698151</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>515579</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7099451</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk. Här finns murkna björkhögstubbar för talltitans bohål.</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132698178</v>
+      </c>
+      <c r="B68" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>515664</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7099466</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132698179</v>
+      </c>
+      <c r="B69" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>515644</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7099629</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132698180</v>
+      </c>
+      <c r="B70" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>515465</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7099425</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132698195</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>515658</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7099621</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132698145</v>
+      </c>
+      <c r="B72" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>515573</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7099479</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Flera frökapslar och gröna blad på fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132698160</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lill-Skarvhöjden Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>515607</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7099550</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18475-2026 artfynd.xlsx
+++ b/artfynd/A 18475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614862</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614864</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614866</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614872</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614874</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614875</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698197</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698198</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614837</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614839</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614840</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614842</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2279,6 +2354,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698146</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698147</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698159</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2637,6 +2727,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698188</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2744,6 +2839,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698190</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2865,6 +2965,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698200</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2991,6 +3096,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3117,6 +3227,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698202</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3353,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698203</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3364,6 +3484,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3490,6 +3615,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698205</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3611,6 +3741,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698206</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3732,6 +3867,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698207</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3863,6 +4003,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3960,6 +4105,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614867</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4057,6 +4207,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614868</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4154,6 +4309,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614869</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4251,6 +4411,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614870</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4348,6 +4513,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614871</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4469,6 +4639,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698162</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4590,6 +4765,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698163</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4725,6 +4905,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698164</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4855,6 +5040,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698166</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4976,6 +5166,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698167</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5106,6 +5301,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698169</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5227,6 +5427,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698170</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5362,6 +5567,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698172</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5483,6 +5693,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698173</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5604,6 +5819,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698174</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5729,6 +5949,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698154</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5859,6 +6084,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698156</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5994,6 +6224,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698157</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6119,6 +6354,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698158</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6245,6 +6485,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698175</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6375,6 +6620,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698176</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6505,6 +6755,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698177</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6607,6 +6862,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614863</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6709,6 +6969,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614843</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6811,6 +7076,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614845</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6913,6 +7183,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614846</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7015,6 +7290,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614847</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7117,6 +7397,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614848</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7219,6 +7504,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614849</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7321,6 +7611,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132614850</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7456,6 +7751,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698148</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7591,6 +7891,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698149</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7726,6 +8031,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698150</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7850,6 +8160,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698196</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7972,6 +8287,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698183</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8094,6 +8414,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698184</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8216,6 +8541,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698186</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8339,6 +8669,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698151</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8450,6 +8785,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698178</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8561,6 +8901,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698179</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8672,6 +9017,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698180</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8800,6 +9150,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698195</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8916,6 +9271,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698145</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9023,8 +9383,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698160</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>